--- a/program.xlsx
+++ b/program.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `findMax` function iterates through an integer array to find and return its largest element.</t>
+          <t>The `findMax` function iterates through an array of integers to find and return the largest value.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | An array of integers in which to find the maximum value. | The number of elements in the `arr` array. |</t>
+          <t>Description | An array of integers from which the maximum value will be found. | The total number of elements in the `arr` array. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function identifies the maximum value within an integer array. It begins by assuming the first element of the array, `arr[0]`, is the maximum and assigns it to a local variable `max`. The function then enters a `for` loop that iterates through the rest of the array elements, starting from the second element (`i = 1`) up to the element at index `size - 1`. In each iteration, it compares the current element `arr[i]` with the value stored in `max`. If `arr[i]` is greater than `max`, the fun...</t>
+          <t>This function provides a straightforward way to determine the maximum value within an integer array. The logic begins by initializing a local variable `max` with the value of the first element in the array, `arr[0]`. It then enters a `for` loop that iterates through the remaining elements of the array, starting from the second element at index `1` up to the element at index `size - 1`. Inside the loop, each element `arr[i]` is compared to the current `max` value. If `arr[i]` is greater than `...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The array `arr` should not be empty. The function accesses `arr[0]` without checking if `size` is greater than 0. Passing an empty array (with `size` as 0) will result in undefined behavior. - The `size` parameter must accurately represent the number of elements in the array to prevent reading from memory outside the array's bounds. - The function works correctly with arrays containing positive, negative, and zero values. **Output Example**: A single integer representing the largest value i...</t>
+          <t>- The input array `arr` should not be empty. The function accesses `arr[0]` without checking if `size` is 0, which will lead to undefined behavior if the array is empty. - The `size` parameter must accurately reflect the number of elements in the array to prevent out-of-bounds memory access. **Output Example**: The function returns a single integer representing the highest value found in the array. For an input array `{10, 5, 45, 12, 8}`, the function would return `45`.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `stringLength` function calculates the length of a null-terminated string, excluding the final null character.</t>
+          <t>The `stringLength` function calculates the length of a null-terminated string by counting the number of characters before the null terminator.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- **`str`** (`char[]`): A character array representing the C-style string. This string must be properly terminated with a null character (`\0`).</t>
+          <t>- **`str`** `char[]`: A character array representing the C-style string whose length is to be measured.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a manual implementation for determining the length of a C-style string. It operates by iterating through the characters of the input array `str` until it encounters the null terminator (`\0`), which signifies the end of the string. The function initializes an integer counter, `length`, to `0`. It then enters a `while` loop that continues as long as the character at the current index, `str[length]`, is not the null character. Inside the loop, the `length` variable is inc...</t>
+          <t>This function provides a manual implementation for determining the length of a C-style string. It operates based on the principle that strings in C are terminated by a special null character, `\0`. The function initializes an integer counter, `length`, to `0`. It then enters a `while` loop that iterates through the input character array `str`. The loop continues as long as the character at the current index, `str[length]`, is not the null terminator `\0`. Inside the loop, the `length` variabl...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The input character array `str` **must** be null-terminated. Failure to provide a null-terminated string will cause the function to read beyond the bounds of the array, leading to undefined behavior and potential program crashes. - The returned length does not include the null terminator character `\0` in its count. - The function does not modify the content of the input string `str`. **Output Example**: The function returns an integer representing the number of characters in the string. Fo...</t>
+          <t>- The input array `str` must be properly null-terminated. If the null terminator `\0` is missing, the function will continue to read beyond the bounds of the array, leading to undefined behavior and a potential program crash. - The length returned by the function does not include the final null terminator character. For example, the string `"abc"` has a length of 3. **Output Example**: The function returns an integer representing the number of characters in the string. For the input `"Hello"`...</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: `int` - The integer to be checked for primality.</t>
+          <t>- `n`: An `int` representing the integer to be checked for primality.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function implements a primality test to verify if the input number `n` is prime. The logic proceeds as follows: 1. **Base Case Check**: The function first checks if `n` is less than or equal to 1. By definition, numbers less than or equal to 1 are not considered prime numbers, so the function immediately returns `false`. 2. **Iterative Division Check**: A `for` loop is initiated to check for potential divisors. The loop starts with `i = 2` and continues as long as `i * i &lt;= n`. This cond...</t>
+          <t>This function implements an efficient trial division algorithm to test if a number `n` is prime. The logic proceeds as follows: 1. First, it handles the base cases. By definition, prime numbers must be greater than 1. The function checks if `n &lt;= 1`. If this condition is true, it immediately returns `false`. 2. If `n` is greater than 1, the function enters a `for` loop that iterates from `i = 2` up to the square root of `n`. The condition `i * i &lt;= n` is a common optimization; if `n` has a di...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The function correctly handles edge cases by returning `false` for any integer less than or equal to 1. - The function uses an efficient trial division algorithm, which is suitable for moderately sized integers. - The return type is `bool`. To use the `bool`, `true`, and `false` keywords in C, you must include the `&lt;stdbool.h&gt;` header. **Output Example**: The function returns a boolean value. For an input of `29`, the output would be:</t>
+          <t>- The function returns a boolean value (`true` or `false`) which requires including the `&lt;stdbool.h&gt;` header in C. - The input number `n` must be an integer. The function correctly handles non-positive integers by returning `false`. - This implementation is efficient for moderately sized integers but may be slow for very large numbers. **Output Example**: A possible return value for a prime number input.</t>
         </is>
       </c>
     </row>
@@ -631,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `main` function serves as the entry point for the program, demonstrating the usage of three utility functions: `findMax`, `stringLength`, and `isPrime`.</t>
+          <t>The `main` function serves as the entry point for the program, demonstrating the usage of three distinct utility functions: `findMax`, `stringLength`, and `isPrime`.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>This function does not accept any parameters.</t>
+          <t>This function does not accept any command-line arguments.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>The `main` function executes a sequence of operations to showcase the functionality of other helper functions within the program. 1. **Find Maximum in an Array**: * An integer array `nums` is initialized with the values `{5, 12, 3, 19, 7}`. * The variable `size` is calculated by dividing the total size of the `nums` array by the size of a single integer element, effectively determining the number of elements in the array. * It then calls the `findMax` function, passing `nums` and `size` as ar...</t>
+          <t>The `main` function executes a sequence of operations to showcase the functionality of other helper functions within the program. 1. **Finding the Maximum Number**: * An integer array named `nums` is initialized with the values `{5, 12, 3, 19, 7}`. * The variable `size` is calculated to determine the number of elements in the `nums` array. This is achieved by dividing the total size of the array (`sizeof(nums)`) by the size of a single element (`sizeof(nums[0])`). * The `findMax` function is ...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This function is the primary entry point for the C program. - It depends on the external functions `findMax`, `stringLength`, and `isPrime`. These functions must be defined and linked for the program to compile and run correctly. - All results are printed directly to the standard output (the console). **Output Example**: The function will print the results of the function calls to the console.</t>
+          <t>- This `main` function is designed as a driver to test and demonstrate other functions. - For this code to compile and run, the functions `findMax`, `stringLength`, and `isPrime` must be defined elsewhere in the project. - The output is sent to the standard output stream (typically the console). - The `&lt;stdio.h&gt;` header is required for the `printf` function. **Output Example**: The function will print the results of the function calls directly to the console.</t>
         </is>
       </c>
     </row>

--- a/program.xlsx
+++ b/program.xlsx
@@ -461,12 +461,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -531,17 +531,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | An array of integers from which the maximum value will be found. | The total number of elements in the `arr` array. |</t>
+          <t>Description | The input array of integers to be searched. | The total number of elements in the `arr`. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to determine the maximum value within an integer array. The logic begins by initializing a local variable `max` with the value of the first element in the array, `arr[0]`. It then enters a `for` loop that iterates through the remaining elements of the array, starting from the second element at index `1` up to the element at index `size - 1`. Inside the loop, each element `arr[i]` is compared to the current `max` value. If `arr[i]` is greater than `...</t>
+          <t>This function provides a straightforward way to determine the maximum value within an integer array. The logic begins by initializing a variable `max` with the value of the first element of the array, `arr[0]`. It then proceeds to loop through the remaining elements of the array, starting from the second element at index `1` up to the last element specified by `size`. Inside the loop, each element `arr[i]` is compared to the current `max` value. If the current element `arr[i]` is greater than...</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- The input array `arr` should not be empty. The function accesses `arr[0]` without checking if `size` is 0, which will lead to undefined behavior if the array is empty. - The `size` parameter must accurately reflect the number of elements in the array to prevent out-of-bounds memory access. **Output Example**: The function returns a single integer representing the highest value found in the array. For an input array `{10, 5, 45, 12, 8}`, the function would return `45`.</t>
+          <t>Important points to consider when using this function: - The `size` parameter must accurately reflect the number of elements in the `arr` to prevent out-of-bounds memory access or incorrect results. - The function assumes the array is not empty. Passing an array with `size` as 0 will result in undefined behavior due to the initial access of `arr[0]`. - The function works with both positive and negative integers. **Output Example**: The function returns a single integer representing the maximu...</t>
         </is>
       </c>
     </row>
@@ -556,27 +556,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>stringLength(str[])</t>
+          <t>findMin(arr[], size)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `stringLength` function calculates the length of a null-terminated string by counting the number of characters before the null terminator.</t>
+          <t>The `findMin` function iterates through an array of integers to find and return the smallest value.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- **`str`** `char[]`: A character array representing the C-style string whose length is to be measured.</t>
+          <t>Description | The array of integers to be searched. | The number of elements in the `arr` array. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function provides a manual implementation for determining the length of a C-style string. It operates based on the principle that strings in C are terminated by a special null character, `\0`. The function initializes an integer counter, `length`, to `0`. It then enters a `while` loop that iterates through the input character array `str`. The loop continues as long as the character at the current index, `str[length]`, is not the null terminator `\0`. Inside the loop, the `length` variabl...</t>
+          <t>The `findMin` function provides a straightforward way to determine the minimum value within an integer array. The function begins by initializing a local integer variable `min` with the value of the first element of the array, `arr[0]`. This variable serves as the initial candidate for the minimum value. It then enters a `for` loop that iterates through the array, starting from the second element (index `1`) up to, but not including, the `size` of the array. In each iteration, it compares the...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The input array `str` must be properly null-terminated. If the null terminator `\0` is missing, the function will continue to read beyond the bounds of the array, leading to undefined behavior and a potential program crash. - The length returned by the function does not include the final null terminator character. For example, the string `"abc"` has a length of 3. **Output Example**: The function returns an integer representing the number of characters in the string. For the input `"Hello"`...</t>
+          <t>- The function assumes the array is not empty. Passing an array with `size` as 0 or less will result in undefined behavior due to the initial access of `arr[0]`. - The `size` parameter must accurately represent the number of elements in `arr`. An incorrect size can lead to either not all elements being checked or reading from memory outside the array's bounds. - The function correctly handles arrays containing positive, negative, and zero values. **Output Example**: The function returns a sin...</t>
         </is>
       </c>
     </row>
@@ -591,27 +591,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>isPrime(n)</t>
+          <t>calculateAverage(arr[], size)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `isPrime` function determines whether a given integer is a prime number.</t>
+          <t>The `calculateAverage` function computes the arithmetic mean of the elements in a given integer array.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n`: An `int` representing the integer to be checked for primality.</t>
+          <t>Description | An array of integers for which the average will be calculated. | The total number of elements in the `arr` array. |</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function implements an efficient trial division algorithm to test if a number `n` is prime. The logic proceeds as follows: 1. First, it handles the base cases. By definition, prime numbers must be greater than 1. The function checks if `n &lt;= 1`. If this condition is true, it immediately returns `false`. 2. If `n` is greater than 1, the function enters a `for` loop that iterates from `i = 2` up to the square root of `n`. The condition `i * i &lt;= n` is a common optimization; if `n` has a di...</t>
+          <t>This function provides a straightforward way to calculate the average of a list of integers. It operates by first initializing an integer variable `sum` to `0`. It then enters a `for` loop that iterates from `i = 0` up to, but not including, the `size` of the array. In each iteration, the value of the current element `arr[i]` is added to the `sum`. After the loop has processed all elements, the function calculates the final average. To ensure a precise floating-point result and avoid integer ...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- The function returns a boolean value (`true` or `false`) which requires including the `&lt;stdbool.h&gt;` header in C. - The input number `n` must be an integer. The function correctly handles non-positive integers by returning `false`. - This implementation is efficient for moderately sized integers but may be slow for very large numbers. **Output Example**: A possible return value for a prime number input.</t>
+          <t>- The `size` parameter must be greater than zero. Passing `size` as `0` will result in a division-by-zero error, leading to undefined behavior. - The value of `size` should accurately represent the number of elements in the `arr` array to prevent incorrect calculations or memory access errors. - The function returns a `double` to accurately represent averages that are not whole numbers. **Output Example**: A floating-point number representing the calculated average.</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,128 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>stringLength(str[])</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>The `stringLength` function calculates the length of a null-terminated string by counting the number of characters before the null terminator.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>- `str`: A `char[]` array representing the null-terminated string whose length is to be determined.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>This function provides a manual implementation for calculating the length of a C-style string. It operates based on the fundamental principle that strings in C are sequences of characters terminated by a special null character (`\0`). The function initializes an integer counter, `length`, to `0`. It then enters a `while` loop that iterates through the input character array `str`. The loop's condition, `str[length] != '\0'`, checks if the character at the current index (`length`) is the null t...</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- The input array `str` **must** be a valid null-terminated string. If the null terminator `\0` is missing, the function will continue to read beyond the bounds of the array, leading to undefined behavior and potential program crashes. - The length returned by the function does not include the null terminator `\0` in its count. - The function does not modify the content of the input string `str`. **Output Example**: For an input string `"Hello"`, which is stored in memory as `['H', 'e', 'l', ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>getRandom(min, max)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `getRandom` function generates a pseudo-random integer within a specified inclusive range.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Description | The minimum possible value for the random number (inclusive). | The maximum possible value for the random number (inclusive). |</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a reliable way to obtain a random integer between two boundary values, `min` and `max`. The function first ensures that the range boundaries are correctly ordered. It checks if `min` is greater than `max`. If this condition is true, it swaps the two values using a temporary variable `temp`. This makes the function robust, as it will work correctly even if the arguments are passed in the wrong order. The core of the function is the expression `min + rand() % (max - min +...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- This function depends on the standard C `rand()` function. For generating different sequences of random numbers across program executions, it is essential to seed the random number generator once at the start of your program using `srand()`. A common practice is to seed it with the current time: `srand(time(NULL));`. - The range is inclusive, meaning the returned value can be equal to `min` or `max`. - The function automatically handles cases where `min` is provided as a larger value than `...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>isPrime(n)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>The `isPrime` function determines whether a given integer is a prime number.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>This function provides an efficient method to check if an integer `n` is a prime number. The logic begins by handling the base cases. According to the definition of prime numbers, any integer less than or equal to 1 is not prime. The function reflects this by immediately returning `false` if `n &lt;= 1`. For numbers greater than 1, the function iterates from `i = 2` up to the square root of `n`. The condition `i * i &lt;= n` is an optimization that avoids checking divisors beyond the square root of...</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>- The function correctly identifies that numbers less than or equal to 1 are not prime. - The return type is `bool`. In C, this will evaluate to `true` (typically 1) or `false` (typically 0). - This implementation is efficient for moderately sized integers. **Output Example**: The function returns a boolean value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>main</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `main` function serves as the entry point for the program, demonstrating the usage of three distinct utility functions: `findMax`, `stringLength`, and `isPrime`.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>This function does not accept any command-line arguments.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>The `main` function executes a sequence of operations to showcase the functionality of other helper functions within the program. 1. **Finding the Maximum Number**: * An integer array named `nums` is initialized with the values `{5, 12, 3, 19, 7}`. * The variable `size` is calculated to determine the number of elements in the `nums` array. This is achieved by dividing the total size of the array (`sizeof(nums)`) by the size of a single element (`sizeof(nums[0])`). * The `findMax` function is ...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- This `main` function is designed as a driver to test and demonstrate other functions. - For this code to compile and run, the functions `findMax`, `stringLength`, and `isPrime` must be defined elsewhere in the project. - The output is sent to the standard output stream (typically the console). - The `&lt;stdio.h&gt;` header is required for the `printf` function. **Output Example**: The function will print the results of the function calls directly to the console.</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The `main` function serves as the entry point for the program, demonstrating the usage of several utility functions: `findMax`, `stringLength`, and `isPrime`.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>This function does not accept any parameters upon execution.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>The `main` function orchestrates a series of operations to showcase the functionality of other helper functions within the program. 1. **Find Maximum in an Array**: - An integer array `nums` is initialized with the values `{5, 12, 3, 19, 7}`. - The `size` of the array is calculated by dividing the total memory occupied by the array (`sizeof(nums)`) by the memory size of a single element (`sizeof(nums[0])`). - The `findMax` function is called with the `nums` array and its `size`. The result, w...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>- This function is the primary entry point for the C program and is automatically called when the program starts. - It depends on three external functions: `findMax`, `stringLength`, and `isPrime`. These functions must be defined and linked for the program to compile and run correctly. - The `printf` function is used for output, which requires including the standard I/O library header (`&lt;stdio.h&gt;`). **Output Example**: The console output when the program is executed, assuming the helper funct...</t>
         </is>
       </c>
     </row>

--- a/program.xlsx
+++ b/program.xlsx
@@ -467,10 +467,10 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,26 +524,10 @@
           <t>findMax(arr[], size)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>The `findMax` function iterates through an array of integers to find and return the largest value.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Description | The input array of integers to be searched. | The total number of elements in the `arr`. |</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to determine the maximum value within an integer array. The logic begins by initializing a variable `max` with the value of the first element of the array, `arr[0]`. It then proceeds to loop through the remaining elements of the array, starting from the second element at index `1` up to the last element specified by `size`. Inside the loop, each element `arr[i]` is compared to the current `max` value. If the current element `arr[i]` is greater than...</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Important points to consider when using this function: - The `size` parameter must accurately reflect the number of elements in the `arr` to prevent out-of-bounds memory access or incorrect results. - The function assumes the array is not empty. Passing an array with `size` as 0 will result in undefined behavior due to the initial access of `arr[0]`. - The function works with both positive and negative integers. **Output Example**: The function returns a single integer representing the maximu...</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -559,26 +543,10 @@
           <t>findMin(arr[], size)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `findMin` function iterates through an array of integers to find and return the smallest value.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Description | The array of integers to be searched. | The number of elements in the `arr` array. |</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>The `findMin` function provides a straightforward way to determine the minimum value within an integer array. The function begins by initializing a local integer variable `min` with the value of the first element of the array, `arr[0]`. This variable serves as the initial candidate for the minimum value. It then enters a `for` loop that iterates through the array, starting from the second element (index `1`) up to, but not including, the `size` of the array. In each iteration, it compares the...</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- The function assumes the array is not empty. Passing an array with `size` as 0 or less will result in undefined behavior due to the initial access of `arr[0]`. - The `size` parameter must accurately represent the number of elements in `arr`. An incorrect size can lead to either not all elements being checked or reading from memory outside the array's bounds. - The function correctly handles arrays containing positive, negative, and zero values. **Output Example**: The function returns a sin...</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -594,26 +562,10 @@
           <t>calculateAverage(arr[], size)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `calculateAverage` function computes the arithmetic mean of the elements in a given integer array.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Description | An array of integers for which the average will be calculated. | The total number of elements in the `arr` array. |</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a straightforward way to calculate the average of a list of integers. It operates by first initializing an integer variable `sum` to `0`. It then enters a `for` loop that iterates from `i = 0` up to, but not including, the `size` of the array. In each iteration, the value of the current element `arr[i]` is added to the `sum`. After the loop has processed all elements, the function calculates the final average. To ensure a precise floating-point result and avoid integer ...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>- The `size` parameter must be greater than zero. Passing `size` as `0` will result in a division-by-zero error, leading to undefined behavior. - The value of `size` should accurately represent the number of elements in the `arr` array to prevent incorrect calculations or memory access errors. - The function returns a `double` to accurately represent averages that are not whole numbers. **Output Example**: A floating-point number representing the calculated average.</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -629,26 +581,10 @@
           <t>stringLength(str[])</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `stringLength` function calculates the length of a null-terminated string by counting the number of characters before the null terminator.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `str`: A `char[]` array representing the null-terminated string whose length is to be determined.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This function provides a manual implementation for calculating the length of a C-style string. It operates based on the fundamental principle that strings in C are sequences of characters terminated by a special null character (`\0`). The function initializes an integer counter, `length`, to `0`. It then enters a `while` loop that iterates through the input character array `str`. The loop's condition, `str[length] != '\0'`, checks if the character at the current index (`length`) is the null t...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- The input array `str` **must** be a valid null-terminated string. If the null terminator `\0` is missing, the function will continue to read beyond the bounds of the array, leading to undefined behavior and potential program crashes. - The length returned by the function does not include the null terminator `\0` in its count. - The function does not modify the content of the input string `str`. **Output Example**: For an input string `"Hello"`, which is stored in memory as `['H', 'e', 'l', ...</t>
-        </is>
-      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -664,26 +600,10 @@
           <t>getRandom(min, max)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `getRandom` function generates a pseudo-random integer within a specified inclusive range.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Description | The minimum possible value for the random number (inclusive). | The maximum possible value for the random number (inclusive). |</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a reliable way to obtain a random integer between two boundary values, `min` and `max`. The function first ensures that the range boundaries are correctly ordered. It checks if `min` is greater than `max`. If this condition is true, it swaps the two values using a temporary variable `temp`. This makes the function robust, as it will work correctly even if the arguments are passed in the wrong order. The core of the function is the expression `min + rand() % (max - min +...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- This function depends on the standard C `rand()` function. For generating different sequences of random numbers across program executions, it is essential to seed the random number generator once at the start of your program using `srand()`. A common practice is to seed it with the current time: `srand(time(NULL));`. - The range is inclusive, meaning the returned value can be equal to `min` or `max`. - The function automatically handles cases where `min` is provided as a larger value than `...</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -699,22 +619,10 @@
           <t>isPrime(n)</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>The `isPrime` function determines whether a given integer is a prime number.</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>This function provides an efficient method to check if an integer `n` is a prime number. The logic begins by handling the base cases. According to the definition of prime numbers, any integer less than or equal to 1 is not prime. The function reflects this by immediately returning `false` if `n &lt;= 1`. For numbers greater than 1, the function iterates from `i = 2` up to the square root of `n`. The condition `i * i &lt;= n` is an optimization that avoids checking divisors beyond the square root of...</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>- The function correctly identifies that numbers less than or equal to 1 are not prime. - The return type is `bool`. In C, this will evaluate to `true` (typically 1) or `false` (typically 0). - This implementation is efficient for moderately sized integers. **Output Example**: The function returns a boolean value.</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -730,26 +638,10 @@
           <t>main</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>The `main` function serves as the entry point for the program, demonstrating the usage of several utility functions: `findMax`, `stringLength`, and `isPrime`.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>This function does not accept any parameters upon execution.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>The `main` function orchestrates a series of operations to showcase the functionality of other helper functions within the program. 1. **Find Maximum in an Array**: - An integer array `nums` is initialized with the values `{5, 12, 3, 19, 7}`. - The `size` of the array is calculated by dividing the total memory occupied by the array (`sizeof(nums)`) by the memory size of a single element (`sizeof(nums[0])`). - The `findMax` function is called with the `nums` array and its `size`. The result, w...</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>- This function is the primary entry point for the C program and is automatically called when the program starts. - It depends on three external functions: `findMax`, `stringLength`, and `isPrime`. These functions must be defined and linked for the program to compile and run correctly. - The `printf` function is used for output, which requires including the standard I/O library header (`&lt;stdio.h&gt;`). **Output Example**: The console output when the program is executed, assuming the helper funct...</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
